--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486984_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486984_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.234</v>
+        <v>7.0963</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1104</v>
+        <v>3.7651</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1237</v>
+        <v>3.3312</v>
       </c>
       <c r="G2" t="n">
         <v>4.2347</v>
@@ -610,13 +610,13 @@
         <v>0.616</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4018</v>
+        <v>1.2641</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4457</v>
+        <v>0.2091</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8475</v>
+        <v>1.055</v>
       </c>
       <c r="V2" t="n">
         <v>2.0082</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2415</v>
+        <v>5.4037</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3685</v>
+        <v>6.2639</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.127</v>
+        <v>-0.8602</v>
       </c>
       <c r="G3" t="n">
         <v>5.2148</v>
@@ -688,13 +688,13 @@
         <v>0.4107</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1438</v>
+        <v>0.0184</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3098</v>
+        <v>0.2052</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4536</v>
+        <v>-0.1868</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2402</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8606</v>
+        <v>5.1893</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2482</v>
+        <v>3.9029</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6124</v>
+        <v>1.2863</v>
       </c>
       <c r="G4" t="n">
         <v>0.5729</v>
@@ -766,13 +766,13 @@
         <v>0.616</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8134</v>
+        <v>1.1421</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8563</v>
+        <v>-0.2016</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6697</v>
+        <v>1.3437</v>
       </c>
       <c r="V4" t="n">
         <v>3.885</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.1042</v>
+        <v>3.5532</v>
       </c>
       <c r="E5" t="n">
-        <v>2.173</v>
+        <v>1.8592</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9312</v>
+        <v>1.694</v>
       </c>
       <c r="G5" t="n">
         <v>0.4211</v>
@@ -844,13 +844,13 @@
         <v>0.4107</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3956</v>
+        <v>0.8446</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5656</v>
+        <v>0.2518</v>
       </c>
       <c r="U5" t="n">
-        <v>0.83</v>
+        <v>0.5928</v>
       </c>
       <c r="V5" t="n">
         <v>1.8768</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3604</v>
+        <v>2.8199</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0048</v>
+        <v>0.3362</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3651</v>
+        <v>2.4837</v>
       </c>
       <c r="G6" t="n">
         <v>2.0957</v>
@@ -922,13 +922,13 @@
         <v>0.4107</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2031</v>
+        <v>0.6626</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4457</v>
+        <v>-0.1047</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.7673</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3491</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1805</v>
+        <v>2.2743</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1731</v>
+        <v>3.0297</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9926</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>1.3603</v>
@@ -1000,13 +1000,13 @@
         <v>0.616</v>
       </c>
       <c r="S7" t="n">
-        <v>0.313</v>
+        <v>0.4068</v>
       </c>
       <c r="T7" t="n">
-        <v>0.457</v>
+        <v>0.3137</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.144</v>
+        <v>0.0931</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1088</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6201</v>
+        <v>1.7798</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1807</v>
+        <v>0.1032</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4395</v>
+        <v>1.6766</v>
       </c>
       <c r="G8" t="n">
         <v>2.0889</v>
@@ -1078,13 +1078,13 @@
         <v>0.616</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5765</v>
+        <v>0.7362</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0118</v>
+        <v>-0.0892</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5883</v>
+        <v>0.8254</v>
       </c>
       <c r="V8" t="n">
         <v>1.4189</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1771</v>
+        <v>0.8229</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3941</v>
+        <v>0.8324</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.217</v>
+        <v>-0.0095</v>
       </c>
       <c r="G9" t="n">
         <v>-0.581</v>
@@ -1156,13 +1156,13 @@
         <v>0.4107</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9983</v>
+        <v>0.6441</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1389</v>
+        <v>0.5772</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1406</v>
+        <v>0.0669</v>
       </c>
       <c r="V9" t="n">
         <v>0.3491</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7937</v>
+        <v>0.8125</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3943</v>
+        <v>0.1464</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3994</v>
+        <v>0.6662</v>
       </c>
       <c r="G10" t="n">
         <v>2.5178</v>
@@ -1234,13 +1234,13 @@
         <v>0.4107</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5963000000000001</v>
+        <v>0.6151</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3021</v>
+        <v>0.0542</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2941</v>
+        <v>0.5609</v>
       </c>
       <c r="V10" t="n">
         <v>0.3491</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5415</v>
+        <v>0.5563</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1705</v>
+        <v>-1.8296</v>
       </c>
       <c r="F11" t="n">
-        <v>2.712</v>
+        <v>2.3859</v>
       </c>
       <c r="G11" t="n">
         <v>-0.5586</v>
@@ -1312,13 +1312,13 @@
         <v>0.2053</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.9096</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5851</v>
+        <v>-0.2442</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4798</v>
+        <v>1.1538</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5361</v>
+        <v>0.3212</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3525</v>
+        <v>-0.182</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.5033</v>
       </c>
       <c r="G12" t="n">
         <v>0.0796</v>
@@ -1390,13 +1390,13 @@
         <v>1.0267</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1341</v>
+        <v>0.9193</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1858</v>
+        <v>0.3563</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9483</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>0.3491</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.0755</v>
+        <v>-1.0672</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6454</v>
+        <v>-0.3703</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4301</v>
+        <v>-0.6969</v>
       </c>
       <c r="G13" t="n">
         <v>-1.4875</v>
@@ -1468,13 +1468,13 @@
         <v>0.4107</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1506</v>
+        <v>-0.1423</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5192</v>
+        <v>-0.2442</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3686</v>
+        <v>0.1019</v>
       </c>
       <c r="V13" t="n">
         <v>1.1786</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>28.5742</v>
+        <v>29.5622</v>
       </c>
       <c r="E14" t="n">
-        <v>16.8691</v>
+        <v>17.8571</v>
       </c>
       <c r="F14" t="n">
-        <v>11.7052</v>
+        <v>11.7051</v>
       </c>
       <c r="G14" t="n">
         <v>15.9587</v>
@@ -1546,13 +1546,13 @@
         <v>6.160200000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>7.032400000000001</v>
+        <v>8.0206</v>
       </c>
       <c r="T14" t="n">
-        <v>0.09540000000000026</v>
+        <v>1.0836</v>
       </c>
       <c r="U14" t="n">
-        <v>6.9368</v>
+        <v>6.936999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>10.7167</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4804</v>
+        <v>0.8893</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1824</v>
+        <v>1.6593</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.702</v>
+        <v>-0.77</v>
       </c>
       <c r="G15" t="n">
         <v>-0.699</v>
@@ -1624,13 +1624,13 @@
         <v>1.4374</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8302</v>
+        <v>0.2392</v>
       </c>
       <c r="T15" t="n">
-        <v>0.612</v>
+        <v>0.089</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2183</v>
+        <v>0.1502</v>
       </c>
       <c r="V15" t="n">
         <v>0.9384</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1446</v>
+        <v>0.2039</v>
       </c>
       <c r="E16" t="n">
         <v>0.7941</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6495</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>1.0973</v>
@@ -1702,13 +1702,13 @@
         <v>0.2053</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3634</v>
+        <v>-0.3042</v>
       </c>
       <c r="T16" t="n">
         <v>-0.2635</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0999</v>
+        <v>-0.0407</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5893</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6762</v>
+        <v>-0.1287</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0709</v>
+        <v>0.1383</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6052999999999999</v>
+        <v>-0.2671</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4933</v>
@@ -1780,13 +1780,13 @@
         <v>0.8214</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1267</v>
+        <v>-0.5792</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7169</v>
+        <v>-0.5077</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4098</v>
+        <v>-0.0716</v>
       </c>
       <c r="V17" t="n">
         <v>0.1224</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8663</v>
+        <v>-1.3755</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6411</v>
+        <v>-0.9549</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2252</v>
+        <v>-0.4205</v>
       </c>
       <c r="G18" t="n">
         <v>0.9912</v>
@@ -1858,13 +1858,13 @@
         <v>0.8214</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3425</v>
+        <v>-0.1666</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2171</v>
+        <v>-0.5309</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5597</v>
+        <v>0.3643</v>
       </c>
       <c r="V18" t="n">
         <v>-1.9947</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2907</v>
+        <v>-1.9123</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9393</v>
+        <v>-1.7301</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3514</v>
+        <v>-0.1822</v>
       </c>
       <c r="G19" t="n">
         <v>-0.3587</v>
@@ -1936,13 +1936,13 @@
         <v>1.2321</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0728</v>
+        <v>-0.6945</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1121</v>
+        <v>-0.9029</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0393</v>
+        <v>0.2084</v>
       </c>
       <c r="V19" t="n">
         <v>-1.8858</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. MILADINOVIC</t>
+          <t>R. TIMONER GIMENEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1408</v>
+        <v>-2.9268</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4159</v>
+        <v>-1.1763</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.5567</v>
+        <v>-1.7506</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5913</v>
+        <v>-2.1544</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1575</v>
+        <v>-0.652</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4338</v>
+        <v>-1.5024</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9546</v>
+        <v>1.0521</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2312</v>
+        <v>0.5129</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7234</v>
+        <v>0.5391</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.5459</v>
+        <v>-3.2064</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3887</v>
+        <v>-1.1649</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.1572</v>
+        <v>-2.0415</v>
       </c>
       <c r="P20" t="n">
-        <v>1.0267</v>
+        <v>0.2053</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2053</v>
+        <v>-1.0267</v>
       </c>
       <c r="R20" t="n">
         <v>1.2321</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0213</v>
+        <v>-0.6287</v>
       </c>
       <c r="T20" t="n">
-        <v>0.07729999999999999</v>
+        <v>-0.8526</v>
       </c>
       <c r="U20" t="n">
-        <v>0.944</v>
+        <v>0.2238</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.5975</v>
+        <v>-0.3491</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5893</v>
+        <v>-0.3491</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.1868</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. TIMONER GIMENEZ</t>
+          <t>G. MILADINOVIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0165</v>
+        <v>-3.9393</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6993</v>
+        <v>0.8928</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3172</v>
+        <v>-4.8322</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1544</v>
+        <v>-2.5913</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.652</v>
+        <v>-1.1575</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5024</v>
+        <v>-1.4338</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0521</v>
+        <v>0.9546</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5129</v>
+        <v>0.2312</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5391</v>
+        <v>0.7234</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.2064</v>
+        <v>-3.5459</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1649</v>
+        <v>-1.3887</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.0415</v>
+        <v>-2.1572</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2053</v>
+        <v>1.0267</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0267</v>
+        <v>-0.2053</v>
       </c>
       <c r="R21" t="n">
         <v>1.2321</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7184</v>
+        <v>0.2227</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3756</v>
+        <v>-0.4457</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3428</v>
+        <v>0.6685</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3491</v>
+        <v>-2.5975</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3491</v>
+        <v>0.5893</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-3.1868</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3442</v>
+        <v>-3.9519</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.3508</v>
+        <v>-3.2462</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-0.7057</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4606</v>
@@ -2170,13 +2170,13 @@
         <v>1.4374</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5522</v>
+        <v>-0.1599</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8177</v>
+        <v>-0.7131</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2655</v>
+        <v>0.5532</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5367</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3565</v>
+        <v>-4.02</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4701</v>
+        <v>-2.6793</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8864</v>
+        <v>-1.3407</v>
       </c>
       <c r="G23" t="n">
         <v>-2.9514</v>
@@ -2248,13 +2248,13 @@
         <v>0.8214</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2791</v>
+        <v>-0.9425</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7518</v>
+        <v>-0.961</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5272</v>
+        <v>0.0185</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9474</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8666</v>
+        <v>-4.3052</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0026</v>
+        <v>-2.8979</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.864</v>
+        <v>-1.4073</v>
       </c>
       <c r="G24" t="n">
         <v>-1.9778</v>
@@ -2326,13 +2326,13 @@
         <v>1.0267</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.9853</v>
+        <v>-1.4239</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3833</v>
+        <v>-1.2787</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.602</v>
+        <v>-0.1452</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6982</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.6413</v>
+        <v>-5.0154</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.9233</v>
+        <v>-2.5049</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.718</v>
+        <v>-2.5105</v>
       </c>
       <c r="G25" t="n">
         <v>-4.3607</v>
@@ -2404,13 +2404,13 @@
         <v>1.0267</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1287</v>
+        <v>-0.5028</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9881</v>
+        <v>-0.5697</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1406</v>
+        <v>0.0669</v>
       </c>
       <c r="V25" t="n">
         <v>-1.1786</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-28.5741</v>
+        <v>-26.4819</v>
       </c>
       <c r="E26" t="n">
-        <v>-11.705</v>
+        <v>-11.7051</v>
       </c>
       <c r="F26" t="n">
-        <v>-16.8691</v>
+        <v>-14.777</v>
       </c>
       <c r="G26" t="n">
         <v>-15.9587</v>
@@ -2482,13 +2482,13 @@
         <v>11.294</v>
       </c>
       <c r="S26" t="n">
-        <v>-7.0326</v>
+        <v>-4.940399999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-6.936800000000001</v>
+        <v>-6.9368</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.09550000000000008</v>
+        <v>1.9963</v>
       </c>
       <c r="V26" t="n">
         <v>-10.7165</v>
